--- a/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición</t>
+          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,88; 36,74</t>
+          <t>31,92; 36,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,59; 38,58</t>
+          <t>33,32; 38,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,32; 39,68</t>
+          <t>32,73; 39,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,11; 40,61</t>
+          <t>34,85; 40,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,98; 39,81</t>
+          <t>34,02; 39,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,2; 45,73</t>
+          <t>37,69; 45,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,29; 37,84</t>
+          <t>34,24; 37,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,67; 38,6</t>
+          <t>34,67; 38,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,19; 42,17</t>
+          <t>36,14; 42,23</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,06; 34,63</t>
+          <t>31,2; 34,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,51; 36,44</t>
+          <t>32,57; 36,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,41; 39,1</t>
+          <t>33,33; 39,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,84; 37,03</t>
+          <t>33,1; 37,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 37,11</t>
+          <t>33,14; 37,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,53; 46,16</t>
+          <t>37,95; 45,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,58; 35,34</t>
+          <t>32,61; 35,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,46; 36,15</t>
+          <t>33,41; 36,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,04; 42,34</t>
+          <t>37,01; 42,51</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,62; 36,03</t>
+          <t>31,53; 36,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,87; 34,72</t>
+          <t>30,92; 34,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,38; 56,0</t>
+          <t>36,99; 54,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,63; 35,96</t>
+          <t>31,55; 36,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,69; 34,79</t>
+          <t>30,62; 34,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,17; 44,21</t>
+          <t>36,36; 44,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,21; 35,38</t>
+          <t>32,23; 35,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,27; 34,16</t>
+          <t>31,35; 34,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,16; 51,82</t>
+          <t>38,22; 50,53</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,1; 37,81</t>
+          <t>33,18; 38,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,39; 36,55</t>
+          <t>32,17; 36,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,62</t>
+          <t>33,21; 40,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,61; 38,28</t>
+          <t>33,65; 38,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,51; 37,85</t>
+          <t>33,64; 38,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,53; 44,98</t>
+          <t>36,58; 44,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,01; 37,14</t>
+          <t>34,02; 37,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,56; 36,54</t>
+          <t>33,62; 36,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,69; 41,36</t>
+          <t>35,98; 41,39</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,02; 35,16</t>
+          <t>33,07; 35,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,25; 35,31</t>
+          <t>33,28; 35,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,17; 46,03</t>
+          <t>36,26; 45,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,33; 36,62</t>
+          <t>34,34; 36,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,02</t>
+          <t>33,95; 36,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,76; 42,84</t>
+          <t>38,64; 42,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,0; 35,5</t>
+          <t>34,05; 35,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,94; 35,45</t>
+          <t>33,88; 35,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,19; 43,09</t>
+          <t>38,18; 43,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
+          <t>Peso medio, en kilogramos, recogido por medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,92; 36,65</t>
+          <t>32,15; 36,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,32; 38,15</t>
+          <t>33,61; 38,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,73; 39,79</t>
+          <t>32,65; 39,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,85; 40,23</t>
+          <t>35,12; 40,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,02; 39,85</t>
+          <t>34,12; 39,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,69; 45,46</t>
+          <t>37,31; 46,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,24; 37,82</t>
+          <t>34,15; 37,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,67; 38,46</t>
+          <t>34,65; 38,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,14; 42,23</t>
+          <t>36,63; 42,42</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,2; 34,9</t>
+          <t>31,3; 35,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,57; 36,41</t>
+          <t>32,59; 36,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,33; 39,01</t>
+          <t>33,32; 39,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,1; 37,04</t>
+          <t>32,92; 36,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,14; 37,08</t>
+          <t>33,18; 37,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,95; 45,9</t>
+          <t>37,51; 45,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,61; 35,59</t>
+          <t>32,47; 35,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,41; 36,18</t>
+          <t>33,31; 36,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,01; 42,51</t>
+          <t>36,78; 42,51</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,53; 36,08</t>
+          <t>31,66; 36,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,92; 34,86</t>
+          <t>30,86; 34,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,99; 54,66</t>
+          <t>37,2; 55,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,55; 36,1</t>
+          <t>31,37; 36,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,62; 34,66</t>
+          <t>30,77; 34,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,36; 44,31</t>
+          <t>36,07; 43,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,23; 35,34</t>
+          <t>32,25; 35,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,35; 34,27</t>
+          <t>31,26; 34,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,22; 50,53</t>
+          <t>38,37; 51,32</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,18; 38,03</t>
+          <t>33,13; 37,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,17; 36,44</t>
+          <t>32,46; 36,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,21; 40,4</t>
+          <t>33,69; 40,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,65; 38,16</t>
+          <t>33,77; 38,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,64; 38,05</t>
+          <t>33,62; 37,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,58; 44,34</t>
+          <t>36,8; 44,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,02; 37,16</t>
+          <t>34,22; 37,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,62; 36,64</t>
+          <t>33,6; 36,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,98; 41,39</t>
+          <t>35,9; 41,07</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,07; 35,17</t>
+          <t>32,85; 35,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 35,26</t>
+          <t>33,24; 35,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,26; 45,96</t>
+          <t>36,26; 46,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,34; 36,69</t>
+          <t>34,36; 36,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,95; 36,18</t>
+          <t>33,86; 36,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,64; 42,94</t>
+          <t>38,81; 42,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,05; 35,59</t>
+          <t>34,06; 35,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,88; 35,38</t>
+          <t>33,9; 35,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,18; 43,06</t>
+          <t>38,35; 43,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36,74</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42,84</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>34,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>35,85</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,74</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,42</t>
+          <t>36,32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39,22</t>
+          <t>40,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,15; 36,91</t>
+          <t>35,11; 40,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,61; 38,37</t>
+          <t>33,98; 39,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,65; 39,72</t>
+          <t>38,57; 47,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,12; 40,4</t>
+          <t>31,88; 36,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,12; 39,93</t>
+          <t>33,59; 38,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,31; 46,06</t>
+          <t>32,64; 40,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,15; 37,9</t>
+          <t>34,29; 37,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,65; 38,32</t>
+          <t>34,67; 38,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,63; 42,42</t>
+          <t>37,19; 43,08</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34,89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,05</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42,12</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>33,03</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>34,41</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36,02</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34,89</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>35,05</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,28</t>
+          <t>36,94</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39,27</t>
+          <t>40,08</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,3; 35,09</t>
+          <t>32,84; 37,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,59; 36,43</t>
+          <t>32,89; 37,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,32; 39,15</t>
+          <t>38,47; 46,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,92; 36,88</t>
+          <t>31,06; 34,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,18; 37,45</t>
+          <t>32,51; 36,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,51; 45,97</t>
+          <t>34,29; 39,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,47; 35,33</t>
+          <t>32,58; 35,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,31; 36,19</t>
+          <t>33,46; 36,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,78; 42,51</t>
+          <t>37,93; 43,02</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32,63</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40,64</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>33,75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>32,85</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>45,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,67</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,63</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,74</t>
+          <t>39,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42,8</t>
+          <t>39,97</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,66; 36,0</t>
+          <t>31,63; 35,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,86; 34,75</t>
+          <t>30,69; 34,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,2; 55,25</t>
+          <t>36,98; 45,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,37; 36,06</t>
+          <t>31,62; 36,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,77; 34,79</t>
+          <t>30,87; 34,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 43,93</t>
+          <t>35,62; 44,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,25; 35,33</t>
+          <t>32,21; 35,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,26; 34,05</t>
+          <t>31,27; 34,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,37; 51,32</t>
+          <t>37,44; 43,22</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35,93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,65</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40,63</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>35,22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,31</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35,93</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,65</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,11</t>
+          <t>37,99</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38,46</t>
+          <t>39,27</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,13; 37,53</t>
+          <t>33,61; 38,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,46; 36,62</t>
+          <t>33,51; 37,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,69; 40,41</t>
+          <t>37,11; 45,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,77; 38,16</t>
+          <t>33,1; 37,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,62; 37,87</t>
+          <t>32,39; 36,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,8; 44,54</t>
+          <t>34,92; 41,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 37,08</t>
+          <t>34,01; 37,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,6; 36,61</t>
+          <t>33,56; 36,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,9; 41,07</t>
+          <t>36,82; 41,98</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,57</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>34,06</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>34,29</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>39,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>35,45</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,67</t>
+          <t>37,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40,02</t>
+          <t>39,83</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,85; 35,06</t>
+          <t>34,33; 36,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,24; 35,3</t>
+          <t>33,92; 36,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,26; 46,47</t>
+          <t>39,65; 43,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,36; 36,64</t>
+          <t>33,02; 35,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,86; 36,12</t>
+          <t>33,25; 35,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,81; 42,98</t>
+          <t>35,93; 39,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,06; 35,59</t>
+          <t>34,0; 35,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,9; 35,41</t>
+          <t>33,94; 35,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,35; 43,54</t>
+          <t>38,44; 41,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36,74</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34,3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,85</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,32</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,98</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36,32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40,07</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>37.57859214412968</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>36.74459405257701</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>42.83620117876841</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>34.29739877756896</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>35.85056421078085</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>36.32254735218088</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>35.97830022186288</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>36.32441978478515</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>40.07095767077509</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>35,11; 40,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33,98; 39,81</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>38,57; 47,16</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31,88; 36,74</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33,59; 38,58</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,64; 40,15</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,29; 37,84</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34,67; 38,6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37,19; 43,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>35.10527176016399</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>33.97813316189644</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>38.56985570242744</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>31.87875911680214</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>33.59246994557915</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>32.63801313943097</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>34.29165254864458</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>34.67344905410702</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>37.18978890853119</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>40.61265579019992</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>39.80723173161102</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>47.1621262143109</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>36.7442521253075</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>38.58277326474504</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>40.14976346211488</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>37.84391187516761</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>38.6019052918833</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>43.07929295217328</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>34,89</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>35,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>42,12</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33,03</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>34,41</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,94</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,99</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>34,74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>32,84; 37,03</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>32,89; 37,11</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38,47; 46,71</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31,06; 34,63</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>32,51; 36,44</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,29; 39,99</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,58; 35,34</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33,46; 36,15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>37,93; 43,02</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>34.88500532959285</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>35.05225982010151</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>42.12141738532258</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>33.02971474169073</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>34.41084750255088</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>36.93719868420425</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>33.98764394092473</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>34.74235845270113</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>40.07503253990217</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>33,67</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>32,63</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,75</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,85</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,15</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,71</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32,73</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39,97</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>32.83595957505879</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>32.88776700514824</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>38.47159047488883</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>31.06254230848192</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>32.50821644076738</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>34.28944503147637</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>32.57589573281702</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>33.45787399604749</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>37.93085206408604</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>31,63; 35,96</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30,69; 34,79</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36,98; 45,18</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31,62; 36,03</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>30,87; 34,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>35,62; 44,11</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>32,21; 35,38</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>31,27; 34,16</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37,44; 43,22</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>37.03028423939647</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>37.1125610247381</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>46.70792253267344</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>34.6278493938348</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>36.44170866937869</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>39.99029673493649</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>35.33947411751691</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>36.15274097896271</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>43.02390638031356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>35,93</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>35,65</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40,63</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35,22</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>34,31</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,99</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,58</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35,01</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39,27</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>33.67405996838801</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>32.62610936371258</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>40.63509254779081</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>33.75065849732542</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>32.84921563849881</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>39.15236984108552</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>33.71140976098088</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>32.73209865675144</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>39.96669886704873</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>33,61; 38,28</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33,51; 37,85</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37,11; 45,33</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33,1; 37,81</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>32,39; 36,55</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,92; 41,62</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,01; 37,14</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33,56; 36,54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36,82; 41,98</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>31.63241546915582</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>30.69028246326734</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>36.98036677644266</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>31.61816659336601</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>30.87495993403324</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>35.62154977853928</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>32.21076521420311</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>31.27319402598394</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>37.43934687597227</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>35.9591600825368</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>34.78811256512108</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>45.18105646463889</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>36.02959578408093</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>34.71675796589527</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>44.11048245116017</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>35.38244298393093</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>34.16241982865311</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>43.21611194108206</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>35.92666012692826</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>35.65180875786946</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>40.62681612628055</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>35.2189470264055</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>34.3072662659126</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>37.9893830520639</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>35.57681725993711</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>35.00743393453847</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>39.26781030270575</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>33.60829696690323</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>33.5129718999647</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>37.11397043089251</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>33.09537420526572</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>32.39398911782834</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>34.92366973354713</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>34.01239110175248</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>33.56313298257433</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>36.81823833997984</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>38.27660045268595</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>37.84516787294132</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>45.32929802207617</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>37.81488046029502</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>36.54624034942375</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>41.61665694036986</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>37.14304802766587</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>36.53527434804153</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>41.97601477294074</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>35,45</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>34,98</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41,57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,29</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,77</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34,65</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>34,33; 36,62</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33,92; 36,02</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39,65; 43,6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33,02; 35,16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33,25; 35,31</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,93; 39,45</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,0; 35,5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33,94; 35,45</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38,44; 41,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>35.44843435005416</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>34.98302810569339</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>41.57133812767115</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>34.05725872658873</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>34.28930529698515</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>37.67013959233078</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>34.76911694347378</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>34.65166167910315</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>39.83460484424268</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>34.3267834308165</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>33.92413600596117</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>39.64719022744256</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>33.01926233159483</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>33.25006435481784</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>35.92751210078502</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>33.99698655297402</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>33.93870104361312</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>38.44355676125927</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>36.61512912221778</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>36.01709270789181</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>43.59954962486894</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>35.16099858478962</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>35.3139747648505</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>39.44922824487214</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>35.49591031272644</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>35.45095558898304</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>41.19932662360646</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
